--- a/ML-Entrees/ig/StructureDefinition-fr-lm-observation-pregnancy.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-observation-pregnancy.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="135">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-14T07:59:58+00:00</t>
+    <t>2026-04-16T07:11:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -304,39 +304,43 @@
     <t>fr-lm-observation-pregnancy.header.author[x].authorProfessional</t>
   </si>
   <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-personne-structure-auteur
+</t>
+  </si>
+  <si>
+    <t>L'auteur est un professionnel de santé</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.author[x].authorProfessional</t>
+  </si>
+  <si>
+    <t>fr-lm-observation-pregnancy.header.author[x].authorOrganisation</t>
+  </si>
+  <si>
+    <t>L'auteur est une organisation</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.author[x].authorOrganisation</t>
+  </si>
+  <si>
+    <t>fr-lm-observation-pregnancy.header.author[x].authorDevice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-systeme-structure-auteur
+</t>
+  </si>
+  <si>
+    <t>L'auteur est un système</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.author[x].authorDevice</t>
+  </si>
+  <si>
+    <t>fr-lm-observation-pregnancy.header.performer</t>
+  </si>
+  <si>
     <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-personne-structure
 </t>
-  </si>
-  <si>
-    <t>L'auteur est un professionnel de santé</t>
-  </si>
-  <si>
-    <t>fr-lm-entry.header.author[x].authorProfessional</t>
-  </si>
-  <si>
-    <t>fr-lm-observation-pregnancy.header.author[x].authorOrganisation</t>
-  </si>
-  <si>
-    <t>L'auteur est une organisation</t>
-  </si>
-  <si>
-    <t>fr-lm-entry.header.author[x].authorOrganisation</t>
-  </si>
-  <si>
-    <t>fr-lm-observation-pregnancy.header.author[x].authorDevice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-systeme-structure-auteur
-</t>
-  </si>
-  <si>
-    <t>L'auteur est un système</t>
-  </si>
-  <si>
-    <t>fr-lm-entry.header.author[x].authorDevice</t>
-  </si>
-  <si>
-    <t>fr-lm-observation-pregnancy.header.performer</t>
   </si>
   <si>
     <t>Exécutant (performer)</t>
@@ -742,7 +746,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="78.91015625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="79.609375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1707,13 +1711,13 @@
         <v>73</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1764,7 +1768,7 @@
         <v>73</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>74</v>
@@ -1781,10 +1785,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1807,13 +1811,13 @@
         <v>73</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -1864,7 +1868,7 @@
         <v>73</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>74</v>
@@ -1881,10 +1885,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -1907,13 +1911,13 @@
         <v>73</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -1964,7 +1968,7 @@
         <v>73</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>74</v>
@@ -1981,10 +1985,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2007,13 +2011,13 @@
         <v>73</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2064,7 +2068,7 @@
         <v>73</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>74</v>
@@ -2081,10 +2085,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2107,13 +2111,13 @@
         <v>73</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2164,7 +2168,7 @@
         <v>73</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>74</v>
@@ -2181,10 +2185,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2207,13 +2211,13 @@
         <v>73</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2264,7 +2268,7 @@
         <v>73</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>74</v>
@@ -2281,10 +2285,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2307,13 +2311,13 @@
         <v>73</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2364,7 +2368,7 @@
         <v>73</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -2381,10 +2385,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2407,13 +2411,13 @@
         <v>73</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2464,7 +2468,7 @@
         <v>73</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -2481,10 +2485,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2507,13 +2511,13 @@
         <v>73</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2564,7 +2568,7 @@
         <v>73</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
